--- a/data/final/series/bcb_sgs_ibc_br_sa.xlsx
+++ b/data/final/series/bcb_sgs_ibc_br_sa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,7 +437,7 @@
         <v>44408</v>
       </c>
       <c r="B2" t="n">
-        <v>96.42256999999999</v>
+        <v>96.31464</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         <v>44439</v>
       </c>
       <c r="B3" t="n">
-        <v>97.03115</v>
+        <v>97.07568000000001</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +453,7 @@
         <v>44469</v>
       </c>
       <c r="B4" t="n">
-        <v>96.97727</v>
+        <v>96.95968999999999</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +461,7 @@
         <v>44500</v>
       </c>
       <c r="B5" t="n">
-        <v>97.49541000000001</v>
+        <v>97.48142</v>
       </c>
     </row>
     <row r="6">
@@ -469,7 +469,7 @@
         <v>44530</v>
       </c>
       <c r="B6" t="n">
-        <v>99.05485</v>
+        <v>98.97262000000001</v>
       </c>
     </row>
     <row r="7">
@@ -477,7 +477,7 @@
         <v>44561</v>
       </c>
       <c r="B7" t="n">
-        <v>99.30268</v>
+        <v>99.35339</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v>44592</v>
       </c>
       <c r="B8" t="n">
-        <v>97.42644</v>
+        <v>97.34401</v>
       </c>
     </row>
     <row r="9">
@@ -493,7 +493,7 @@
         <v>44620</v>
       </c>
       <c r="B9" t="n">
-        <v>98.38327</v>
+        <v>98.43725000000001</v>
       </c>
     </row>
     <row r="10">
@@ -501,7 +501,7 @@
         <v>44651</v>
       </c>
       <c r="B10" t="n">
-        <v>99.5587</v>
+        <v>99.55981</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>44681</v>
       </c>
       <c r="B11" t="n">
-        <v>99.56286</v>
+        <v>99.51646</v>
       </c>
     </row>
     <row r="12">
@@ -517,7 +517,7 @@
         <v>44712</v>
       </c>
       <c r="B12" t="n">
-        <v>99.67480999999999</v>
+        <v>99.67415</v>
       </c>
     </row>
     <row r="13">
@@ -525,7 +525,7 @@
         <v>44742</v>
       </c>
       <c r="B13" t="n">
-        <v>99.51873000000001</v>
+        <v>99.6343</v>
       </c>
     </row>
     <row r="14">
@@ -533,7 +533,7 @@
         <v>44773</v>
       </c>
       <c r="B14" t="n">
-        <v>101.41705</v>
+        <v>101.27684</v>
       </c>
     </row>
     <row r="15">
@@ -541,7 +541,7 @@
         <v>44804</v>
       </c>
       <c r="B15" t="n">
-        <v>101.1048</v>
+        <v>101.07328</v>
       </c>
     </row>
     <row r="16">
@@ -549,7 +549,7 @@
         <v>44834</v>
       </c>
       <c r="B16" t="n">
-        <v>101.15658</v>
+        <v>101.17973</v>
       </c>
     </row>
     <row r="17">
@@ -557,7 +557,7 @@
         <v>44865</v>
       </c>
       <c r="B17" t="n">
-        <v>101.44313</v>
+        <v>101.46342</v>
       </c>
     </row>
     <row r="18">
@@ -565,7 +565,7 @@
         <v>44895</v>
       </c>
       <c r="B18" t="n">
-        <v>100.70751</v>
+        <v>100.66227</v>
       </c>
     </row>
     <row r="19">
@@ -573,7 +573,7 @@
         <v>44926</v>
       </c>
       <c r="B19" t="n">
-        <v>100.45671</v>
+        <v>100.58196</v>
       </c>
     </row>
     <row r="20">
@@ -581,7 +581,7 @@
         <v>44957</v>
       </c>
       <c r="B20" t="n">
-        <v>100.1131</v>
+        <v>100.05178</v>
       </c>
     </row>
     <row r="21">
@@ -589,7 +589,7 @@
         <v>44985</v>
       </c>
       <c r="B21" t="n">
-        <v>102.99794</v>
+        <v>103.00964</v>
       </c>
     </row>
     <row r="22">
@@ -597,7 +597,7 @@
         <v>45016</v>
       </c>
       <c r="B22" t="n">
-        <v>103.10183</v>
+        <v>103.09341</v>
       </c>
     </row>
     <row r="23">
@@ -605,7 +605,7 @@
         <v>45046</v>
       </c>
       <c r="B23" t="n">
-        <v>104.18587</v>
+        <v>104.1626</v>
       </c>
     </row>
     <row r="24">
@@ -613,7 +613,7 @@
         <v>45077</v>
       </c>
       <c r="B24" t="n">
-        <v>102.46133</v>
+        <v>102.3642</v>
       </c>
     </row>
     <row r="25">
@@ -621,7 +621,7 @@
         <v>45107</v>
       </c>
       <c r="B25" t="n">
-        <v>102.39681</v>
+        <v>102.50431</v>
       </c>
     </row>
     <row r="26">
@@ -629,7 +629,7 @@
         <v>45138</v>
       </c>
       <c r="B26" t="n">
-        <v>102.86628</v>
+        <v>102.83357</v>
       </c>
     </row>
     <row r="27">
@@ -637,7 +637,7 @@
         <v>45169</v>
       </c>
       <c r="B27" t="n">
-        <v>102.48117</v>
+        <v>102.45222</v>
       </c>
     </row>
     <row r="28">
@@ -645,7 +645,7 @@
         <v>45199</v>
       </c>
       <c r="B28" t="n">
-        <v>102.49422</v>
+        <v>102.57885</v>
       </c>
     </row>
     <row r="29">
@@ -653,7 +653,7 @@
         <v>45230</v>
       </c>
       <c r="B29" t="n">
-        <v>102.81544</v>
+        <v>102.87707</v>
       </c>
     </row>
     <row r="30">
@@ -661,7 +661,7 @@
         <v>45260</v>
       </c>
       <c r="B30" t="n">
-        <v>103.57529</v>
+        <v>103.528</v>
       </c>
     </row>
     <row r="31">
@@ -669,7 +669,7 @@
         <v>45291</v>
       </c>
       <c r="B31" t="n">
-        <v>104.68308</v>
+        <v>104.8991</v>
       </c>
     </row>
     <row r="32">
@@ -677,7 +677,7 @@
         <v>45322</v>
       </c>
       <c r="B32" t="n">
-        <v>104.47997</v>
+        <v>104.53245</v>
       </c>
     </row>
     <row r="33">
@@ -685,7 +685,7 @@
         <v>45351</v>
       </c>
       <c r="B33" t="n">
-        <v>104.63436</v>
+        <v>104.75961</v>
       </c>
     </row>
     <row r="34">
@@ -693,7 +693,7 @@
         <v>45382</v>
       </c>
       <c r="B34" t="n">
-        <v>104.71934</v>
+        <v>104.7097</v>
       </c>
     </row>
     <row r="35">
@@ -701,7 +701,7 @@
         <v>45412</v>
       </c>
       <c r="B35" t="n">
-        <v>104.96661</v>
+        <v>104.75682</v>
       </c>
     </row>
     <row r="36">
@@ -709,7 +709,7 @@
         <v>45443</v>
       </c>
       <c r="B36" t="n">
-        <v>105.66388</v>
+        <v>105.70704</v>
       </c>
     </row>
     <row r="37">
@@ -717,7 +717,7 @@
         <v>45473</v>
       </c>
       <c r="B37" t="n">
-        <v>106.57692</v>
+        <v>106.57623</v>
       </c>
     </row>
     <row r="38">
@@ -725,7 +725,7 @@
         <v>45504</v>
       </c>
       <c r="B38" t="n">
-        <v>106.95254</v>
+        <v>106.88756</v>
       </c>
     </row>
     <row r="39">
@@ -733,7 +733,7 @@
         <v>45535</v>
       </c>
       <c r="B39" t="n">
-        <v>107.13607</v>
+        <v>107.14396</v>
       </c>
     </row>
     <row r="40">
@@ -741,7 +741,7 @@
         <v>45565</v>
       </c>
       <c r="B40" t="n">
-        <v>107.99994</v>
+        <v>107.99916</v>
       </c>
     </row>
     <row r="41">
@@ -749,7 +749,7 @@
         <v>45596</v>
       </c>
       <c r="B41" t="n">
-        <v>108.20756</v>
+        <v>108.15356</v>
       </c>
     </row>
     <row r="42">
@@ -757,7 +757,7 @@
         <v>45626</v>
       </c>
       <c r="B42" t="n">
-        <v>107.96783</v>
+        <v>107.98489</v>
       </c>
     </row>
     <row r="43">
@@ -765,7 +765,7 @@
         <v>45657</v>
       </c>
       <c r="B43" t="n">
-        <v>107.1418</v>
+        <v>107.44467</v>
       </c>
     </row>
     <row r="44">
@@ -773,7 +773,7 @@
         <v>45688</v>
       </c>
       <c r="B44" t="n">
-        <v>108.21392</v>
+        <v>108.06979</v>
       </c>
     </row>
     <row r="45">
@@ -781,7 +781,7 @@
         <v>45716</v>
       </c>
       <c r="B45" t="n">
-        <v>108.74593</v>
+        <v>108.77346</v>
       </c>
     </row>
     <row r="46">
@@ -789,7 +789,7 @@
         <v>45747</v>
       </c>
       <c r="B46" t="n">
-        <v>110.20451</v>
+        <v>110.09056</v>
       </c>
     </row>
     <row r="47">
@@ -797,7 +797,7 @@
         <v>45777</v>
       </c>
       <c r="B47" t="n">
-        <v>110.0593</v>
+        <v>109.72323</v>
       </c>
     </row>
     <row r="48">
@@ -805,7 +805,7 @@
         <v>45808</v>
       </c>
       <c r="B48" t="n">
-        <v>109.08727</v>
+        <v>109.00057</v>
       </c>
     </row>
     <row r="49">
@@ -813,7 +813,7 @@
         <v>45838</v>
       </c>
       <c r="B49" t="n">
-        <v>108.85988</v>
+        <v>108.76683</v>
       </c>
     </row>
     <row r="50">
@@ -821,7 +821,7 @@
         <v>45869</v>
       </c>
       <c r="B50" t="n">
-        <v>108.41316</v>
+        <v>108.27053</v>
       </c>
     </row>
     <row r="51">
@@ -829,7 +829,7 @@
         <v>45900</v>
       </c>
       <c r="B51" t="n">
-        <v>108.83964</v>
+        <v>108.80021</v>
       </c>
     </row>
     <row r="52">
@@ -837,7 +837,7 @@
         <v>45930</v>
       </c>
       <c r="B52" t="n">
-        <v>108.76251</v>
+        <v>108.63642</v>
       </c>
     </row>
     <row r="53">
@@ -845,7 +845,7 @@
         <v>45961</v>
       </c>
       <c r="B53" t="n">
-        <v>108.78795</v>
+        <v>108.7159</v>
       </c>
     </row>
     <row r="54">
@@ -853,7 +853,7 @@
         <v>45991</v>
       </c>
       <c r="B54" t="n">
-        <v>109.30007</v>
+        <v>109.27405</v>
       </c>
     </row>
     <row r="55">
@@ -861,7 +861,7 @@
         <v>46022</v>
       </c>
       <c r="B55" t="n">
-        <v>109.27117</v>
+        <v>109.41762</v>
       </c>
     </row>
     <row r="56">
@@ -869,7 +869,7 @@
         <v>46053</v>
       </c>
       <c r="B56" t="n">
-        <v>110.09703</v>
+        <v>110.05486</v>
       </c>
     </row>
     <row r="57">
@@ -877,7 +877,7 @@
         <v>46081</v>
       </c>
       <c r="B57" t="n">
-        <v>110.78559</v>
+        <v>110.65892</v>
       </c>
     </row>
     <row r="58">
@@ -885,7 +885,7 @@
         <v>46112</v>
       </c>
       <c r="B58" t="n">
-        <v>110.58589</v>
+        <v>110.51078</v>
       </c>
     </row>
     <row r="59">
@@ -893,7 +893,15 @@
         <v>46142</v>
       </c>
       <c r="B59" t="n">
-        <v>111.15205</v>
+        <v>110.95732</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B60" t="n">
+        <v>111.03587</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/bcb_sgs_ibc_br_sa.xlsx
+++ b/data/final/series/bcb_sgs_ibc_br_sa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,473 +434,465 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="B2" t="n">
-        <v>96.31464</v>
+        <v>97.07568000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="B3" t="n">
-        <v>97.07568000000001</v>
+        <v>96.95968999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="B4" t="n">
-        <v>96.95968999999999</v>
+        <v>97.48142</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B5" t="n">
-        <v>97.48142</v>
+        <v>98.97262000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B6" t="n">
-        <v>98.97262000000001</v>
+        <v>99.35339</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B7" t="n">
-        <v>99.35339</v>
+        <v>97.34401</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B8" t="n">
-        <v>97.34401</v>
+        <v>98.43725000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B9" t="n">
-        <v>98.43725000000001</v>
+        <v>99.55981</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B10" t="n">
-        <v>99.55981</v>
+        <v>99.51646</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B11" t="n">
-        <v>99.51646</v>
+        <v>99.67415</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B12" t="n">
-        <v>99.67415</v>
+        <v>99.6343</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B13" t="n">
-        <v>99.6343</v>
+        <v>101.27684</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B14" t="n">
-        <v>101.27684</v>
+        <v>101.07328</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B15" t="n">
-        <v>101.07328</v>
+        <v>101.17973</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B16" t="n">
-        <v>101.17973</v>
+        <v>101.46342</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B17" t="n">
-        <v>101.46342</v>
+        <v>100.66227</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B18" t="n">
-        <v>100.66227</v>
+        <v>100.58196</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B19" t="n">
-        <v>100.58196</v>
+        <v>100.05178</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B20" t="n">
-        <v>100.05178</v>
+        <v>103.00964</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B21" t="n">
-        <v>103.00964</v>
+        <v>103.09341</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B22" t="n">
-        <v>103.09341</v>
+        <v>104.1626</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B23" t="n">
-        <v>104.1626</v>
+        <v>102.3642</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B24" t="n">
-        <v>102.3642</v>
+        <v>102.50431</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B25" t="n">
-        <v>102.50431</v>
+        <v>102.83357</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B26" t="n">
-        <v>102.83357</v>
+        <v>102.45222</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B27" t="n">
-        <v>102.45222</v>
+        <v>102.57885</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B28" t="n">
-        <v>102.57885</v>
+        <v>102.87707</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B29" t="n">
-        <v>102.87707</v>
+        <v>103.528</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B30" t="n">
-        <v>103.528</v>
+        <v>104.8991</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B31" t="n">
-        <v>104.8991</v>
+        <v>104.53245</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B32" t="n">
-        <v>104.53245</v>
+        <v>104.75961</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B33" t="n">
-        <v>104.75961</v>
+        <v>104.7097</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B34" t="n">
-        <v>104.7097</v>
+        <v>104.75682</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B35" t="n">
-        <v>104.75682</v>
+        <v>105.70704</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B36" t="n">
-        <v>105.70704</v>
+        <v>106.57623</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B37" t="n">
-        <v>106.57623</v>
+        <v>106.88756</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B38" t="n">
-        <v>106.88756</v>
+        <v>107.14396</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B39" t="n">
-        <v>107.14396</v>
+        <v>107.99916</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B40" t="n">
-        <v>107.99916</v>
+        <v>108.15356</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B41" t="n">
-        <v>108.15356</v>
+        <v>107.98489</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B42" t="n">
-        <v>107.98489</v>
+        <v>107.44467</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B43" t="n">
-        <v>107.44467</v>
+        <v>108.06979</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B44" t="n">
-        <v>108.06979</v>
+        <v>108.77346</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B45" t="n">
-        <v>108.77346</v>
+        <v>110.09056</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B46" t="n">
-        <v>110.09056</v>
+        <v>109.72323</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B47" t="n">
-        <v>109.72323</v>
+        <v>109.00057</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B48" t="n">
-        <v>109.00057</v>
+        <v>108.76683</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B49" t="n">
-        <v>108.76683</v>
+        <v>108.27053</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B50" t="n">
-        <v>108.27053</v>
+        <v>108.80021</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B51" t="n">
-        <v>108.80021</v>
+        <v>108.63642</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B52" t="n">
-        <v>108.63642</v>
+        <v>108.7159</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B53" t="n">
-        <v>108.7159</v>
+        <v>109.27405</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B54" t="n">
-        <v>109.27405</v>
+        <v>109.41762</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B55" t="n">
-        <v>109.41762</v>
+        <v>110.05486</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B56" t="n">
-        <v>110.05486</v>
+        <v>110.65892</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B57" t="n">
-        <v>110.65892</v>
+        <v>110.51078</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B58" t="n">
-        <v>110.51078</v>
+        <v>110.95732</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B59" t="n">
-        <v>110.95732</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B60" t="n">
         <v>111.03587</v>
       </c>
     </row>

--- a/data/final/series/bcb_sgs_ibc_br_sa.xlsx
+++ b/data/final/series/bcb_sgs_ibc_br_sa.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/final/series/bcb_sgs_ibc_br_sa.xlsx
+++ b/data/final/series/bcb_sgs_ibc_br_sa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,7 +437,7 @@
         <v>44439</v>
       </c>
       <c r="B2" t="n">
-        <v>97.07568000000001</v>
+        <v>97.01608</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         <v>44469</v>
       </c>
       <c r="B3" t="n">
-        <v>96.95968999999999</v>
+        <v>96.95313</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +453,7 @@
         <v>44500</v>
       </c>
       <c r="B4" t="n">
-        <v>97.48142</v>
+        <v>97.47790999999999</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +461,7 @@
         <v>44530</v>
       </c>
       <c r="B5" t="n">
-        <v>98.97262000000001</v>
+        <v>99.05295</v>
       </c>
     </row>
     <row r="6">
@@ -469,7 +469,7 @@
         <v>44561</v>
       </c>
       <c r="B6" t="n">
-        <v>99.35339</v>
+        <v>99.36759000000001</v>
       </c>
     </row>
     <row r="7">
@@ -477,7 +477,7 @@
         <v>44592</v>
       </c>
       <c r="B7" t="n">
-        <v>97.34401</v>
+        <v>97.41759</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v>44620</v>
       </c>
       <c r="B8" t="n">
-        <v>98.43725000000001</v>
+        <v>98.48287000000001</v>
       </c>
     </row>
     <row r="9">
@@ -493,7 +493,7 @@
         <v>44651</v>
       </c>
       <c r="B9" t="n">
-        <v>99.55981</v>
+        <v>99.54331000000001</v>
       </c>
     </row>
     <row r="10">
@@ -501,7 +501,7 @@
         <v>44681</v>
       </c>
       <c r="B10" t="n">
-        <v>99.51646</v>
+        <v>99.44726</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>44712</v>
       </c>
       <c r="B11" t="n">
-        <v>99.67415</v>
+        <v>99.65249</v>
       </c>
     </row>
     <row r="12">
@@ -517,7 +517,7 @@
         <v>44742</v>
       </c>
       <c r="B12" t="n">
-        <v>99.6343</v>
+        <v>99.53077999999999</v>
       </c>
     </row>
     <row r="13">
@@ -525,7 +525,7 @@
         <v>44773</v>
       </c>
       <c r="B13" t="n">
-        <v>101.27684</v>
+        <v>101.43252</v>
       </c>
     </row>
     <row r="14">
@@ -533,7 +533,7 @@
         <v>44804</v>
       </c>
       <c r="B14" t="n">
-        <v>101.07328</v>
+        <v>101.09886</v>
       </c>
     </row>
     <row r="15">
@@ -541,7 +541,7 @@
         <v>44834</v>
       </c>
       <c r="B15" t="n">
-        <v>101.17973</v>
+        <v>101.15209</v>
       </c>
     </row>
     <row r="16">
@@ -549,7 +549,7 @@
         <v>44865</v>
       </c>
       <c r="B16" t="n">
-        <v>101.46342</v>
+        <v>101.43094</v>
       </c>
     </row>
     <row r="17">
@@ -557,7 +557,7 @@
         <v>44895</v>
       </c>
       <c r="B17" t="n">
-        <v>100.66227</v>
+        <v>100.7113</v>
       </c>
     </row>
     <row r="18">
@@ -565,7 +565,7 @@
         <v>44926</v>
       </c>
       <c r="B18" t="n">
-        <v>100.58196</v>
+        <v>100.58566</v>
       </c>
     </row>
     <row r="19">
@@ -573,7 +573,7 @@
         <v>44957</v>
       </c>
       <c r="B19" t="n">
-        <v>100.05178</v>
+        <v>100.10937</v>
       </c>
     </row>
     <row r="20">
@@ -581,7 +581,7 @@
         <v>44985</v>
       </c>
       <c r="B20" t="n">
-        <v>103.00964</v>
+        <v>103.08344</v>
       </c>
     </row>
     <row r="21">
@@ -589,7 +589,7 @@
         <v>45016</v>
       </c>
       <c r="B21" t="n">
-        <v>103.09341</v>
+        <v>103.08526</v>
       </c>
     </row>
     <row r="22">
@@ -597,7 +597,7 @@
         <v>45046</v>
       </c>
       <c r="B22" t="n">
-        <v>104.1626</v>
+        <v>103.96006</v>
       </c>
     </row>
     <row r="23">
@@ -605,7 +605,7 @@
         <v>45077</v>
       </c>
       <c r="B23" t="n">
-        <v>102.3642</v>
+        <v>102.40467</v>
       </c>
     </row>
     <row r="24">
@@ -613,7 +613,7 @@
         <v>45107</v>
       </c>
       <c r="B24" t="n">
-        <v>102.50431</v>
+        <v>102.4398</v>
       </c>
     </row>
     <row r="25">
@@ -621,7 +621,7 @@
         <v>45138</v>
       </c>
       <c r="B25" t="n">
-        <v>102.83357</v>
+        <v>102.89895</v>
       </c>
     </row>
     <row r="26">
@@ -629,7 +629,7 @@
         <v>45169</v>
       </c>
       <c r="B26" t="n">
-        <v>102.45222</v>
+        <v>102.48797</v>
       </c>
     </row>
     <row r="27">
@@ -637,7 +637,7 @@
         <v>45199</v>
       </c>
       <c r="B27" t="n">
-        <v>102.57885</v>
+        <v>102.50227</v>
       </c>
     </row>
     <row r="28">
@@ -645,7 +645,7 @@
         <v>45230</v>
       </c>
       <c r="B28" t="n">
-        <v>102.87707</v>
+        <v>102.83037</v>
       </c>
     </row>
     <row r="29">
@@ -653,7 +653,7 @@
         <v>45260</v>
       </c>
       <c r="B29" t="n">
-        <v>103.528</v>
+        <v>103.58799</v>
       </c>
     </row>
     <row r="30">
@@ -661,7 +661,7 @@
         <v>45291</v>
       </c>
       <c r="B30" t="n">
-        <v>104.8991</v>
+        <v>104.88262</v>
       </c>
     </row>
     <row r="31">
@@ -669,7 +669,7 @@
         <v>45322</v>
       </c>
       <c r="B31" t="n">
-        <v>104.53245</v>
+        <v>104.47589</v>
       </c>
     </row>
     <row r="32">
@@ -677,7 +677,7 @@
         <v>45351</v>
       </c>
       <c r="B32" t="n">
-        <v>104.75961</v>
+        <v>104.67291</v>
       </c>
     </row>
     <row r="33">
@@ -685,7 +685,7 @@
         <v>45382</v>
       </c>
       <c r="B33" t="n">
-        <v>104.7097</v>
+        <v>104.68779</v>
       </c>
     </row>
     <row r="34">
@@ -693,7 +693,7 @@
         <v>45412</v>
       </c>
       <c r="B34" t="n">
-        <v>104.75682</v>
+        <v>104.6751</v>
       </c>
     </row>
     <row r="35">
@@ -701,7 +701,7 @@
         <v>45443</v>
       </c>
       <c r="B35" t="n">
-        <v>105.70704</v>
+        <v>105.5521</v>
       </c>
     </row>
     <row r="36">
@@ -709,7 +709,7 @@
         <v>45473</v>
       </c>
       <c r="B36" t="n">
-        <v>106.57623</v>
+        <v>106.65779</v>
       </c>
     </row>
     <row r="37">
@@ -717,7 +717,7 @@
         <v>45504</v>
       </c>
       <c r="B37" t="n">
-        <v>106.88756</v>
+        <v>107.01873</v>
       </c>
     </row>
     <row r="38">
@@ -725,7 +725,7 @@
         <v>45535</v>
       </c>
       <c r="B38" t="n">
-        <v>107.14396</v>
+        <v>107.16697</v>
       </c>
     </row>
     <row r="39">
@@ -733,7 +733,7 @@
         <v>45565</v>
       </c>
       <c r="B39" t="n">
-        <v>107.99916</v>
+        <v>108.02415</v>
       </c>
     </row>
     <row r="40">
@@ -741,7 +741,7 @@
         <v>45596</v>
       </c>
       <c r="B40" t="n">
-        <v>108.15356</v>
+        <v>108.23273</v>
       </c>
     </row>
     <row r="41">
@@ -749,7 +749,7 @@
         <v>45626</v>
       </c>
       <c r="B41" t="n">
-        <v>107.98489</v>
+        <v>107.99539</v>
       </c>
     </row>
     <row r="42">
@@ -757,7 +757,7 @@
         <v>45657</v>
       </c>
       <c r="B42" t="n">
-        <v>107.44467</v>
+        <v>107.3722</v>
       </c>
     </row>
     <row r="43">
@@ -765,7 +765,7 @@
         <v>45688</v>
       </c>
       <c r="B43" t="n">
-        <v>108.06979</v>
+        <v>108.10202</v>
       </c>
     </row>
     <row r="44">
@@ -773,7 +773,7 @@
         <v>45716</v>
       </c>
       <c r="B44" t="n">
-        <v>108.77346</v>
+        <v>108.64347</v>
       </c>
     </row>
     <row r="45">
@@ -781,7 +781,7 @@
         <v>45747</v>
       </c>
       <c r="B45" t="n">
-        <v>110.09056</v>
+        <v>110.0586</v>
       </c>
     </row>
     <row r="46">
@@ -789,7 +789,7 @@
         <v>45777</v>
       </c>
       <c r="B46" t="n">
-        <v>109.72323</v>
+        <v>109.59971</v>
       </c>
     </row>
     <row r="47">
@@ -797,7 +797,7 @@
         <v>45808</v>
       </c>
       <c r="B47" t="n">
-        <v>109.00057</v>
+        <v>108.80425</v>
       </c>
     </row>
     <row r="48">
@@ -805,7 +805,7 @@
         <v>45838</v>
       </c>
       <c r="B48" t="n">
-        <v>108.76683</v>
+        <v>108.90168</v>
       </c>
     </row>
     <row r="49">
@@ -813,7 +813,7 @@
         <v>45869</v>
       </c>
       <c r="B49" t="n">
-        <v>108.27053</v>
+        <v>108.39998</v>
       </c>
     </row>
     <row r="50">
@@ -821,7 +821,7 @@
         <v>45900</v>
       </c>
       <c r="B50" t="n">
-        <v>108.80021</v>
+        <v>108.79892</v>
       </c>
     </row>
     <row r="51">
@@ -829,7 +829,7 @@
         <v>45930</v>
       </c>
       <c r="B51" t="n">
-        <v>108.63642</v>
+        <v>108.7209</v>
       </c>
     </row>
     <row r="52">
@@ -837,7 +837,7 @@
         <v>45961</v>
       </c>
       <c r="B52" t="n">
-        <v>108.7159</v>
+        <v>108.73364</v>
       </c>
     </row>
     <row r="53">
@@ -845,7 +845,7 @@
         <v>45991</v>
       </c>
       <c r="B53" t="n">
-        <v>109.27405</v>
+        <v>109.24151</v>
       </c>
     </row>
     <row r="54">
@@ -853,7 +853,7 @@
         <v>46022</v>
       </c>
       <c r="B54" t="n">
-        <v>109.41762</v>
+        <v>109.46142</v>
       </c>
     </row>
     <row r="55">
@@ -861,7 +861,7 @@
         <v>46053</v>
       </c>
       <c r="B55" t="n">
-        <v>110.05486</v>
+        <v>110.07661</v>
       </c>
     </row>
     <row r="56">
@@ -869,7 +869,7 @@
         <v>46081</v>
       </c>
       <c r="B56" t="n">
-        <v>110.65892</v>
+        <v>110.77581</v>
       </c>
     </row>
     <row r="57">
@@ -877,7 +877,7 @@
         <v>46112</v>
       </c>
       <c r="B57" t="n">
-        <v>110.51078</v>
+        <v>110.60765</v>
       </c>
     </row>
     <row r="58">
@@ -885,7 +885,7 @@
         <v>46142</v>
       </c>
       <c r="B58" t="n">
-        <v>110.95732</v>
+        <v>110.90086</v>
       </c>
     </row>
     <row r="59">
@@ -893,7 +893,15 @@
         <v>46173</v>
       </c>
       <c r="B59" t="n">
-        <v>111.03587</v>
+        <v>110.93102</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B60" t="n">
+        <v>110.22154</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/bcb_sgs_ibc_br_sa.xlsx
+++ b/data/final/series/bcb_sgs_ibc_br_sa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,473 +434,465 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="B2" t="n">
-        <v>97.01608</v>
+        <v>96.95313</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="B3" t="n">
-        <v>96.95313</v>
+        <v>97.47790999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B4" t="n">
-        <v>97.47790999999999</v>
+        <v>99.05295</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B5" t="n">
-        <v>99.05295</v>
+        <v>99.36759000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B6" t="n">
-        <v>99.36759000000001</v>
+        <v>97.41759</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B7" t="n">
-        <v>97.41759</v>
+        <v>98.48287000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B8" t="n">
-        <v>98.48287000000001</v>
+        <v>99.54331000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B9" t="n">
-        <v>99.54331000000001</v>
+        <v>99.44726</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B10" t="n">
-        <v>99.44726</v>
+        <v>99.65249</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B11" t="n">
-        <v>99.65249</v>
+        <v>99.53077999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B12" t="n">
-        <v>99.53077999999999</v>
+        <v>101.43252</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B13" t="n">
-        <v>101.43252</v>
+        <v>101.09886</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B14" t="n">
-        <v>101.09886</v>
+        <v>101.15209</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B15" t="n">
-        <v>101.15209</v>
+        <v>101.43094</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B16" t="n">
-        <v>101.43094</v>
+        <v>100.7113</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B17" t="n">
-        <v>100.7113</v>
+        <v>100.58566</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B18" t="n">
-        <v>100.58566</v>
+        <v>100.10937</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B19" t="n">
-        <v>100.10937</v>
+        <v>103.08344</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B20" t="n">
-        <v>103.08344</v>
+        <v>103.08526</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B21" t="n">
-        <v>103.08526</v>
+        <v>103.96006</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B22" t="n">
-        <v>103.96006</v>
+        <v>102.40467</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B23" t="n">
-        <v>102.40467</v>
+        <v>102.4398</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B24" t="n">
-        <v>102.4398</v>
+        <v>102.89895</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B25" t="n">
-        <v>102.89895</v>
+        <v>102.48797</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B26" t="n">
-        <v>102.48797</v>
+        <v>102.50227</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B27" t="n">
-        <v>102.50227</v>
+        <v>102.83037</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B28" t="n">
-        <v>102.83037</v>
+        <v>103.58799</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B29" t="n">
-        <v>103.58799</v>
+        <v>104.88262</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B30" t="n">
-        <v>104.88262</v>
+        <v>104.47589</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B31" t="n">
-        <v>104.47589</v>
+        <v>104.67291</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B32" t="n">
-        <v>104.67291</v>
+        <v>104.68779</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B33" t="n">
-        <v>104.68779</v>
+        <v>104.6751</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B34" t="n">
-        <v>104.6751</v>
+        <v>105.5521</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B35" t="n">
-        <v>105.5521</v>
+        <v>106.65779</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B36" t="n">
-        <v>106.65779</v>
+        <v>107.01873</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B37" t="n">
-        <v>107.01873</v>
+        <v>107.16697</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B38" t="n">
-        <v>107.16697</v>
+        <v>108.02415</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B39" t="n">
-        <v>108.02415</v>
+        <v>108.23273</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B40" t="n">
-        <v>108.23273</v>
+        <v>107.99539</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B41" t="n">
-        <v>107.99539</v>
+        <v>107.3722</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B42" t="n">
-        <v>107.3722</v>
+        <v>108.10202</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B43" t="n">
-        <v>108.10202</v>
+        <v>108.64347</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B44" t="n">
-        <v>108.64347</v>
+        <v>110.0586</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B45" t="n">
-        <v>110.0586</v>
+        <v>109.59971</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B46" t="n">
-        <v>109.59971</v>
+        <v>108.80425</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B47" t="n">
-        <v>108.80425</v>
+        <v>108.90168</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B48" t="n">
-        <v>108.90168</v>
+        <v>108.39998</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B49" t="n">
-        <v>108.39998</v>
+        <v>108.79892</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B50" t="n">
-        <v>108.79892</v>
+        <v>108.7209</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B51" t="n">
-        <v>108.7209</v>
+        <v>108.73364</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B52" t="n">
-        <v>108.73364</v>
+        <v>109.24151</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B53" t="n">
-        <v>109.24151</v>
+        <v>109.46142</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B54" t="n">
-        <v>109.46142</v>
+        <v>110.07661</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B55" t="n">
-        <v>110.07661</v>
+        <v>110.77581</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B56" t="n">
-        <v>110.77581</v>
+        <v>110.60765</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B57" t="n">
-        <v>110.60765</v>
+        <v>110.90086</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B58" t="n">
-        <v>110.90086</v>
+        <v>110.93102</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B59" t="n">
-        <v>110.93102</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="B60" t="n">
         <v>110.22154</v>
       </c>
     </row>
